--- a/artfynd/A 31117-2025 artfynd.xlsx
+++ b/artfynd/A 31117-2025 artfynd.xlsx
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115683748</v>
+        <v>115683753</v>
       </c>
       <c r="B2" t="n">
-        <v>56178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100092</v>
+        <v>100015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -766,6 +761,11 @@
           <t>2023-06-21</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Granskad av Espen Jensen samt Johan Eklöf</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -790,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115683744</v>
+        <v>115683748</v>
       </c>
       <c r="B3" t="n">
-        <v>56183</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,26 +801,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -905,42 +900,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115683756</v>
+        <v>115683749</v>
       </c>
       <c r="B4" t="n">
-        <v>56164</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -988,12 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,12 +1013,7 @@
         <v>115683747</v>
       </c>
       <c r="B5" t="n">
-        <v>56181</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,42 +1120,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115683745</v>
+        <v>115683746</v>
       </c>
       <c r="B6" t="n">
-        <v>56183</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>205994</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Sydpipistrell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus pipistrellus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1184,14 +1164,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora vörta 1, Bl</t>
+          <t>Stora vörta 2, Bl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534625</v>
+        <v>534595</v>
       </c>
       <c r="R6" t="n">
-        <v>6230241</v>
+        <v>6230161</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,6 +1204,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granskad av Espen Jensen samt Johan Eklöf</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,15 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115683749</v>
+        <v>115683743</v>
       </c>
       <c r="B7" t="n">
-        <v>56178</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,26 +1246,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1299,14 +1279,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stora vörta 1, Bl</t>
+          <t>Stora vörta 2, Bl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534625</v>
+        <v>534595</v>
       </c>
       <c r="R7" t="n">
-        <v>6230241</v>
+        <v>6230161</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,42 +1345,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115683754</v>
+        <v>115683745</v>
       </c>
       <c r="B8" t="n">
-        <v>56164</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1414,14 +1389,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora vörta 2, Bl</t>
+          <t>Stora vörta 1, Bl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534595</v>
+        <v>534625</v>
       </c>
       <c r="R8" t="n">
-        <v>6230161</v>
+        <v>6230241</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,42 +1455,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115683746</v>
+        <v>115683754</v>
       </c>
       <c r="B9" t="n">
-        <v>56182</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205994</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sydpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pipistrellus pipistrellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1571,11 +1541,6 @@
           <t>2023-06-21</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Granskad av Espen Jensen samt Johan Eklöf</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1600,15 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115683753</v>
+        <v>115683755</v>
       </c>
       <c r="B10" t="n">
-        <v>56174</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,26 +1576,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1649,14 +1609,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora vörta 2, Bl</t>
+          <t>Stora vörta 1, Bl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534595</v>
+        <v>534625</v>
       </c>
       <c r="R10" t="n">
-        <v>6230161</v>
+        <v>6230241</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,17 +1643,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Granskad av Espen Jensen samt Johan Eklöf</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 31117-2025 artfynd.xlsx
+++ b/artfynd/A 31117-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115683753</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115683748</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115683749</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115683747</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115683746</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115683743</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115683745</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1562,6 +1602,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115683754</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1672,8 +1717,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115683755</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>